--- a/public/sample_uploads/deal_investors.xlsx
+++ b/public/sample_uploads/deal_investors.xlsx
@@ -1,79 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Investors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Steps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="yyyy/mm/dd" numFmtId="100"/>
-    <numFmt formatCode="yyyy/mm/dd hh:mm:ss" numFmtId="101"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-      <family val="1"/>
-      <b val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEEFF"/>
-        <bgColor rgb="FFDDEEFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="1">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -123,11 +175,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -162,20 +272,24 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="false"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -204,7 +318,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -213,7 +327,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -222,7 +336,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -293,195 +407,374 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <cols>
-    <col width="26.4" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="14.85" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="11.549999999999999" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="37.949999999999996" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="41.25" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="46.199999999999996" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="19.799999999999997" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="14.85" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="11.549999999999999" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="29.7" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="31.349999999999998" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="23.099999999999998" min="12" max="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Investor Name</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Deal Investor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deal Lead</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Primary Amount (USD)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Secondary Amount (USD)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Pre Money Valuation (USD)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Deal Lead</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Primary Amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Secondary Amount</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Pre Money Valuation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Client History</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>RM Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sample Investor 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Referral</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Met at flagship event</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Allan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sample Investor 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Family Office</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cold outreach</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jane Smith</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Introduced by chairman</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Deal Investor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Deck Sent</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Meeting 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meeting 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sample Investor 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sample Investor 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Deal Investor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Company Advisor</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Investor Advisor</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Update Only</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Reminder Emails</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Reminder Date</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>Acme Capital</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>John Doe</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>Referral</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>VC,Tech</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sample Investor 1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Met at conference; people: A, B, C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sample Investor 1</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Follow-up call to discuss pipeline</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>investor@example.com</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sample Investor 2</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Intro meeting via chairman</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
-  <headerFooter/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>